--- a/vijayas/clarification_prd.xlsx
+++ b/vijayas/clarification_prd.xlsx
@@ -413,9 +413,832 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Ambiguity Score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Clarification Questions</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Response Time</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SKU-1001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>API response time should be under 2 seconds</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Improve user experience and reduce latency</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>≤ 2.5 sec</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>≤ 2 sec</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Uptime</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SKU-1002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>System uptime must be 99.5% monthly</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensure system availability</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>≥ 99%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>≥ 99.9%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amit Verma</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SKU-1003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Automated alerts for critical system failures</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduce downtime and faster issue resolution</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Alert within 10 mins</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alert within 5 mins</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>What defines a 'critical system failure'? Is there a list or severity threshold? Should alerts also cover non-critical failures?</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sneha Reddy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SKU-1004</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Implement multi-factor authentication</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhance system security</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optional MFA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Mandatory MFA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Which types of multi-factor authentication should be implemented (SMS, authenticator app, biometrics, etc.)? Is MFA required for all users or only certain roles?</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arjun Patel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UI Improvement</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SKU-1005</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Improve dashboard layout responsiveness</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Better user interaction</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Works on desktop</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Works on all devices</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>What specific devices/platforms must be supported (mobile, tablet, browser types)? What are the measurable criteria for 'responsiveness' (e.g., load time, adaptive layout, resolution support)?</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kavya Nair</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Data Encryption</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SKU-1006</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Encrypt sensitive data at rest and in transit</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Meet compliance requirements</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AES-128</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AES-256</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul Singh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKU-1007</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Generate downloadable audit reports</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Improve transparency</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Monthly reports</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Weekly reports</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>What information should be included in the audit reports? In which formats should reports be generated (PDF, CSV, etc.)? Who can download the reports (admin, user, auditor)?</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Invoice Accuracy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SKU-1008</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ensure invoice calculation accuracy</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Avoid revenue leakage</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>98% accuracy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>100% accuracy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vikram Joshi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Load Handling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SKU-1009</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support 5,000 concurrent users</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Handle peak traffic</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,000 users</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,000 users</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pooja Mehta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRM Sync</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SKU-1010</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Integrate system with CRM platform</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Improve customer data visibility</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Daily sync</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Real-time sync</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Which CRM platforms are to be supported? What data needs to be synchronized (customer records, transactions, etc.)? What is meant by 'real-time sync' (interval, triggers, latency)? Is the integration one-way or bidirectional?</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vijayas/clarification_prd.xlsx
+++ b/vijayas/clarification_prd.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>What defines a 'critical system failure'? Is there a list or severity threshold? Should alerts also cover non-critical failures?</t>
+          <t>What qualifies as a 'critical system failure'? Who are the recipients of the alerts? Are there specific channels (email, SMS, etc.) for alert delivery?</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Which types of multi-factor authentication should be implemented (SMS, authenticator app, biometrics, etc.)? Is MFA required for all users or only certain roles?</t>
+          <t>Which authentication factors are required (e.g., SMS, app, hardware token)? Is MFA required for all users or only specific roles?</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>What specific devices/platforms must be supported (mobile, tablet, browser types)? What are the measurable criteria for 'responsiveness' (e.g., load time, adaptive layout, resolution support)?</t>
+          <t>What does 'responsiveness' mean in this context (e.g., loading time, adaptive layout)? What devices and screen sizes must be supported? Are there specific performance benchmarks?</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>What information should be included in the audit reports? In which formats should reports be generated (PDF, CSV, etc.)? Who can download the reports (admin, user, auditor)?</t>
+          <t>What information should be included in the audit reports? What file formats are required for download? Who should have access to the reports?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Which CRM platforms are to be supported? What data needs to be synchronized (customer records, transactions, etc.)? What is meant by 'real-time sync' (interval, triggers, latency)? Is the integration one-way or bidirectional?</t>
+          <t>Which CRM platform(s) should be integrated? What data fields are to be synchronized? What defines 'real-time' sync in terms of latency or frequency?</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
